--- a/code/data_management/meta_data_processing.xlsx
+++ b/code/data_management/meta_data_processing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute-my.sharepoint.com/personal/sue_su_alleninstitute_org/Documents/LCpaper/manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF5906D-7507-4880-89EB-C2944D6EC385}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3116327-9C4B-40E6-B1C9-03F8311B8F1D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="7125" windowWidth="29040" windowHeight="15720" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>name</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>code/beh_ephys_analysis/antidromic_funcs.py/analyze_antidromic_responses</t>
+  </si>
+  <si>
+    <t>compute_behavior_metrics</t>
+  </si>
+  <si>
+    <t>behavior/{session_id}_beh_metrics.json</t>
+  </si>
+  <si>
+    <t>code/beh_ephys_analysis/beh_metrics.py</t>
   </si>
 </sst>
 </file>
@@ -296,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -325,6 +334,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -855,7 +870,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
   </sheetData>
   <hyperlinks>
@@ -864,8 +892,10 @@
     <hyperlink ref="E9" r:id="rId3" display="https://github.com/AllenNeuralDynamics/aind-beh-ephys-analysis/blob/main/code/beh_ephys_analysis/ccf_generation.py/make_ccf_tbl" xr:uid="{86200356-EB70-DF4F-8FEA-70F94BCA000B}"/>
     <hyperlink ref="D12" r:id="rId4" xr:uid="{B0B15AFD-795D-BB42-94D1-7DB297F4B456}"/>
     <hyperlink ref="D3" r:id="rId5" xr:uid="{7D29D876-4DBD-834B-A286-6B3C96D33384}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{E9017DD4-36DD-4F45-BB17-7B59F59BC27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/code/data_management/meta_data_processing.xlsx
+++ b/code/data_management/meta_data_processing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute-my.sharepoint.com/personal/sue_su_alleninstitute_org/Documents/LCpaper/manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3116327-9C4B-40E6-B1C9-03F8311B8F1D}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E32813F-12B6-3B41-BCB4-D9C84C09F182}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="7125" windowWidth="29040" windowHeight="15720" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="animal_glm" sheetId="3" r:id="rId3"/>
     <sheet name="all_ccf" sheetId="4" r:id="rId4"/>
     <sheet name="all_dorsal_edge" sheetId="5" r:id="rId5"/>
-    <sheet name="all_probe_location" sheetId="6" r:id="rId6"/>
+    <sheet name="all_FP_location" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>name</t>
   </si>
@@ -218,13 +218,28 @@
   </si>
   <si>
     <t>code/beh_ephys_analysis/beh_metrics.py</t>
+  </si>
+  <si>
+    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main/code/check_L_R.ipynb</t>
+  </si>
+  <si>
+    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main</t>
+  </si>
+  <si>
+    <t>convert_manual_annotation2ccf</t>
+  </si>
+  <si>
+    <t>code/generate_dorsal_edegs.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual annotation of dorsal edge of LC is performed in neuraglancer and converted here to ccf coordinates. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -255,6 +270,20 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -305,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -329,17 +358,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -356,6 +392,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -676,17 +716,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1772B6F7-3758-5747-BB67-BFF3A7BA4434}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="63.8125" customWidth="1"/>
-    <col min="3" max="3" width="35.125" customWidth="1"/>
-    <col min="4" max="4" width="23.1875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="63.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" style="8" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="40.25" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -703,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -718,7 +758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>35</v>
       </c>
@@ -733,7 +773,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -750,7 +790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -765,7 +805,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -780,7 +820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -795,7 +835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -810,7 +850,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -825,7 +865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -840,7 +880,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -855,7 +895,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -870,21 +910,21 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>57</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{23ECD49E-201B-3840-A84D-6A40CA277E94}"/>
@@ -895,23 +935,22 @@
     <hyperlink ref="D13" r:id="rId6" xr:uid="{E9017DD4-36DD-4F45-BB17-7B59F59BC27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EB3044-9E2B-DC46-A8B2-1DB9ED99F9B2}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.6875" customWidth="1"/>
-    <col min="2" max="2" width="32.3125" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="58.8125" customWidth="1"/>
-    <col min="5" max="5" width="34.6875" customWidth="1"/>
+    <col min="4" max="4" width="58.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -928,7 +967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -942,7 +981,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -956,7 +995,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -978,17 +1017,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79812901-A6B2-564A-98EF-B6EC9A0AF142}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50.1875" customWidth="1"/>
-    <col min="3" max="3" width="22.6875" customWidth="1"/>
-    <col min="4" max="4" width="83.8125" customWidth="1"/>
-    <col min="5" max="5" width="31.1875" customWidth="1"/>
-    <col min="6" max="6" width="24.6875" customWidth="1"/>
+    <col min="2" max="2" width="50.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="83.83203125" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1029,17 +1068,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F465CB9-37DB-5742-8039-98F9D3D791D6}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1875" customWidth="1"/>
-    <col min="2" max="2" width="37.8125" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
-    <col min="4" max="4" width="71.6875" customWidth="1"/>
+    <col min="4" max="4" width="71.6640625" customWidth="1"/>
     <col min="5" max="5" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1070,12 +1109,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.5">
+    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
         <v>53</v>
       </c>
       <c r="E20" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1088,9 +1132,54 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AA6A6-C8DA-AF48-AC98-394E26C99DD1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
-  <sheetData/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="94.1640625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{B08C88E9-908A-F447-B1DC-4B10229D2AF8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1098,7 +1187,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B436F805-BB62-4849-8671-E3858B17BED0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/code/data_management/meta_data_processing.xlsx
+++ b/code/data_management/meta_data_processing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute-my.sharepoint.com/personal/sue_su_alleninstitute_org/Documents/LCpaper/manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E32813F-12B6-3B41-BCB4-D9C84C09F182}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC8E653-BA93-4D0E-8118-69B653AC36F4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
   <si>
     <t>name</t>
   </si>
@@ -196,9 +196,6 @@
     <t>\</t>
   </si>
   <si>
-    <t>https://github.com/AllenNeuralDynamics/ibl-ephys-alignment-gui/tree/882940b7e34bf63c939ab67e8307cfba0fa388f9</t>
-  </si>
-  <si>
     <t>src/ephys_alignment_gui/launch_gui.py</t>
   </si>
   <si>
@@ -220,12 +217,6 @@
     <t>code/beh_ephys_analysis/beh_metrics.py</t>
   </si>
   <si>
-    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main/code/check_L_R.ipynb</t>
-  </si>
-  <si>
-    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main</t>
-  </si>
-  <si>
     <t>convert_manual_annotation2ccf</t>
   </si>
   <si>
@@ -233,6 +224,21 @@
   </si>
   <si>
     <t xml:space="preserve">Manual annotation of dorsal edge of LC is performed in neuraglancer and converted here to ccf coordinates. </t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>882940b7e34bf63c939ab67e8307cfba0fa388f9</t>
+  </si>
+  <si>
+    <t>https://github.com/AllenNeuralDynamics/ibl-ephys-alignment-gui</t>
+  </si>
+  <si>
+    <t>764145811bfd21b4d06cfe39e59217082d69d76a</t>
+  </si>
+  <si>
+    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep</t>
   </si>
 </sst>
 </file>
@@ -275,15 +281,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -358,24 +364,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -716,17 +719,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1772B6F7-3758-5747-BB67-BFF3A7BA4434}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="63.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" customWidth="1"/>
-    <col min="4" max="4" width="23.1640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="63.8125" customWidth="1"/>
+    <col min="3" max="3" width="35.125" customWidth="1"/>
+    <col min="4" max="4" width="23.1875" style="8" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="40.1640625" customWidth="1"/>
+    <col min="6" max="6" width="40.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -743,7 +746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -758,7 +761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A3" s="9" t="s">
         <v>35</v>
       </c>
@@ -773,7 +776,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -790,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -802,10 +805,10 @@
         <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -820,7 +823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -835,7 +838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -850,7 +853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -865,7 +868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -880,7 +883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -895,7 +898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -910,21 +913,21 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{23ECD49E-201B-3840-A84D-6A40CA277E94}"/>
@@ -935,22 +938,23 @@
     <hyperlink ref="D13" r:id="rId6" xr:uid="{E9017DD4-36DD-4F45-BB17-7B59F59BC27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EB3044-9E2B-DC46-A8B2-1DB9ED99F9B2}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" customWidth="1"/>
+    <col min="1" max="1" width="39.6875" customWidth="1"/>
+    <col min="2" max="2" width="32.3125" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="58.83203125" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="58.8125" customWidth="1"/>
+    <col min="5" max="5" width="34.6875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -967,7 +971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -981,7 +985,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -992,10 +996,10 @@
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1017,17 +1021,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79812901-A6B2-564A-98EF-B6EC9A0AF142}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50.1640625" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="83.83203125" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="50.1875" customWidth="1"/>
+    <col min="3" max="3" width="22.6875" customWidth="1"/>
+    <col min="4" max="4" width="83.8125" customWidth="1"/>
+    <col min="5" max="5" width="31.1875" customWidth="1"/>
+    <col min="6" max="6" width="24.6875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1044,7 +1048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1068,17 +1072,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F465CB9-37DB-5742-8039-98F9D3D791D6}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="2" width="37.83203125" customWidth="1"/>
-    <col min="3" max="3" width="43.5" customWidth="1"/>
-    <col min="4" max="4" width="71.6640625" customWidth="1"/>
-    <col min="5" max="5" width="40.5" customWidth="1"/>
+    <col min="1" max="1" width="22.1875" customWidth="1"/>
+    <col min="2" max="2" width="19.0625" customWidth="1"/>
+    <col min="3" max="3" width="20.0625" customWidth="1"/>
+    <col min="4" max="4" width="61.5625" customWidth="1"/>
+    <col min="5" max="5" width="34.5" customWidth="1"/>
+    <col min="6" max="6" width="38.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1094,8 +1099,11 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1103,23 +1111,21 @@
         <v>50</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.5">
+      <c r="C20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
       <c r="E20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1127,53 +1133,60 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{98AE4375-52C5-8943-BF9E-A8DC1E11B69F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AA6A6-C8DA-AF48-AC98-394E26C99DD1}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="94.1640625" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" customWidth="1"/>
+    <col min="1" max="1" width="39.6875" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="58.375" customWidth="1"/>
+    <col min="4" max="4" width="29.6875" customWidth="1"/>
+    <col min="5" max="5" width="35.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1187,7 +1200,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B436F805-BB62-4849-8671-E3858B17BED0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/code/data_management/meta_data_processing.xlsx
+++ b/code/data_management/meta_data_processing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute-my.sharepoint.com/personal/sue_su_alleninstitute_org/Documents/LCpaper/manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC8E653-BA93-4D0E-8118-69B653AC36F4}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D177E89F-554C-436C-BDD0-F496F4CD7A1A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
+    <workbookView xWindow="-28920" yWindow="7125" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="all_ccf" sheetId="4" r:id="rId4"/>
     <sheet name="all_dorsal_edge" sheetId="5" r:id="rId5"/>
     <sheet name="all_FP_location" sheetId="6" r:id="rId6"/>
+    <sheet name="np_spatial_crosscorr" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
   <si>
     <t>name</t>
   </si>
@@ -76,12 +77,6 @@
     <t>compute_raw_waveforms</t>
   </si>
   <si>
-    <t>ephys/opto/curated</t>
-  </si>
-  <si>
-    <t>ephys/curated/processed</t>
-  </si>
-  <si>
     <t>ephys/opto/curated/opto_waveforms.zarr</t>
   </si>
   <si>
@@ -139,15 +134,9 @@
     <t>ephys/curated/processed/ccf_unit_locations.csv</t>
   </si>
   <si>
-    <t>ephys/opto/curated/{session_id}_curated_soma_opto_tagging_summary.pkl</t>
-  </si>
-  <si>
     <t>ephys/opto/curated/{session_id}_opto_sigs.pkl</t>
   </si>
   <si>
-    <t>ephys/opto/curated/{session_id}_antidromic_results.pkl</t>
-  </si>
-  <si>
     <t>trial_wise_drift_computation</t>
   </si>
   <si>
@@ -239,6 +228,42 @@
   </si>
   <si>
     <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep</t>
+  </si>
+  <si>
+    <t>ephys/opto/curated/drift,ephys/opto/curated/{session_id}_opto_drift_tbl.csv,ephys/opto/curated/{session_id}_opto_drift_tbl.csv,ephys/opto/curated/{session_id}_motion_drift.pdf,ephys/opto/curated/ {session_id}_drift.pdf</t>
+  </si>
+  <si>
+    <t>ephys/opto/curated/{session_id}_antidromic_results.pkl,ephys/opto/curated/figures/antidromic</t>
+  </si>
+  <si>
+    <t>ephys/opto/curated/figures,ephys/opto/curated/{session_id}_opto_tagging_metrics.pkl,ephys/opto/curated/{session_id}_opto_waveform_metrics.pkl,ephys/opto/curated/{session_id}_opto_tagging.pdf</t>
+  </si>
+  <si>
+    <t>ephys/opto/curated/{session_id}_curated_soma_opto_tagging_summary.pkl,ephys/opto/curated/{session_id}_curated_soma_opto_summary.pdf</t>
+  </si>
+  <si>
+    <t>ephys/curated/processed/{session_id}_curated_auto_corr.pkl,ephys/curated/processed/{session_id}_curated_cross_corr.pkl,ephys/curated/processed/{session_id}_curated_long_corr.png,ephys/curated/processed/{session_id}_curated_short_corr.png</t>
+  </si>
+  <si>
+    <t>{animal_id}_glm_choice_history_model_results.pdf,glm_choice_history_model_results.pkl</t>
+  </si>
+  <si>
+    <t>code/beh_ephys_analysis/lick_video_analysis.py</t>
+  </si>
+  <si>
+    <t>lick_in_trial_model_coefficients_video_False.pdf,lick_in_trial_model_coefficients_video_True.pdf,lick_in_trial_model_coefficients.pdf,lick_in_trial_model_video_False.pkl,lick_in_trial_model_video_True.pkl,lick_train_stats_video_False.pkl,lick_train_stats_video_True.pkl,lick_train_stats.pkl,lick_trains_video_False.pdf,lick_trains_video_True.pdf,lick_trains.pdf</t>
+  </si>
+  <si>
+    <t>clean_up_lick_video_segments</t>
+  </si>
+  <si>
+    <t>compute_spatial_crosscorr</t>
+  </si>
+  <si>
+    <t>band_corr</t>
+  </si>
+  <si>
+    <t>code/beh_ephys_analysis/ephys_spatial_feature.py</t>
   </si>
 </sst>
 </file>
@@ -340,7 +365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -369,12 +394,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -395,10 +414,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,7 +752,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -751,29 +766,29 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A3" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -781,16 +796,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -798,14 +813,14 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -813,44 +828,44 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A7" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -858,14 +873,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -873,14 +888,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
@@ -888,43 +903,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>56</v>
+      <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
@@ -962,7 +977,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -973,44 +988,44 @@
     </row>
     <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="E2" t="s">
         <v>41</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1020,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79812901-A6B2-564A-98EF-B6EC9A0AF142}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1039,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1050,23 +1065,39 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{0027B72A-6E20-6348-8387-03E21E5D1773}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{DC1E97AC-7234-4E30-B624-EB37CCB5165E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1091,7 +1122,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1100,32 +1131,32 @@
         <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.5">
       <c r="C20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +1188,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1165,28 +1196,28 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>61</v>
+      <c r="F1" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
         <v>60</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1194,6 +1225,7 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{B08C88E9-908A-F447-B1DC-4B10229D2AF8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1204,4 +1236,59 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CCC006-4539-441B-882C-29E49D287785}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="20.8125" customWidth="1"/>
+    <col min="4" max="4" width="37.75" customWidth="1"/>
+    <col min="5" max="5" width="42.5" customWidth="1"/>
+    <col min="6" max="6" width="21.0625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{27FFD22E-7285-4055-A0E1-76D6E9947BBB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>